--- a/public/templates/programmes-template.xlsx
+++ b/public/templates/programmes-template.xlsx
@@ -46,6 +46,7 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00374151"/>
       <sz val="10"/>
     </font>
     <font>
@@ -148,9 +149,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -516,11 +515,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -532,6 +532,11 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>programme_type</t>
         </is>
       </c>
     </row>
@@ -546,11 +551,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -584,93 +589,145 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>3. Both name and code must be unique — duplicates will be skipped.</t>
+          <t>3. The same programme CODE can be used with different names (different titles, same code).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>4. Programme codes will be saved in UPPERCASE automatically.</t>
+          <t>4. The same programme NAME can be used with different codes.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>5. Save as CSV: File → Save As → CSV UTF-8 (Comma delimited) (*.csv)</t>
+          <t>5. The combination of name + code must be unique — no exact duplicates.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>6. Go to Bulk Upload → Programme Import and upload the CSV file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+          <t>6. programme_type must be DEGREE or DIPLOMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   DIPLOMA uses Distinction/Credit/Pass classification scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   DEGREE uses First Class/Second Class/Third Class scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>7. Programme codes are saved in UPPERCASE automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>8. Save as CSV: File → Save As → CSV UTF-8 (Comma delimited) (*.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>9. Go to Bulk Upload → Programme Import and upload the CSV file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>COLUMN REFERENCE</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Full programme name — must be unique e.g. Bachelor of Science in Computer Science</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Full programme name (required) — same name can appear with different codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Short programme code — must be unique e.g. BSC_CS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Example: name=Bachelor of Science in Computer Science | code=BSC_CS</t>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Short programme code e.g. BSC_CS (required) — same code can appear with different names</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>programme_type</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>DEGREE or DIPLOMA (required) — controls the classification scale on transcripts</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Example: Bachelor of Science in Computer Science,BSC_CS,DEGREE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="15">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
